--- a/site/ABC-Fitness-ADP-Lyric-Integration-Guide/headings.xlsx
+++ b/site/ABC-Fitness-ADP-Lyric-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pay Data Configuration</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,19 +693,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KPMSJ4R0CKRPGJ98CG93SWPN</t>
+          <t>h_01KPMSJ4R0FP05Q2AS6CBBX3DK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KPMSJ4R0CKRPGJ98CG93SWPN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KPMSJ4R0FP05Q2AS6CBBX3DK</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KPMSJ4R0FP05Q2AS6CBBX3DK</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KPMSJ4R0FP05Q2AS6CBBX3DK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,41 +737,41 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Successful Integration Notification Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
+          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Successful Integration Notification Settings</t>
+          <t>Failed Integration Notification Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Failed Integration Notification Settings</t>
+          <t>Skipped Integration Notification Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Skipped Integration Notification Settings</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,41 +847,41 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
+          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Debug Mode</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,41 +891,41 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KPMSJ4R0KRGFBZT7S9T8WTDZ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KPMSJ4R0KRGFBZT7S9T8WTDZ</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KPMSJ4R0KRGFBZT7S9T8WTDZ</t>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KPMSJ4R0KRGFBZT7S9T8WTDZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,41 +957,41 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,32 +1001,10 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/ABC-Fitness-ADP-Lyric-Integration-Guide/headings.xlsx
+++ b/site/ABC-Fitness-ADP-Lyric-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,139 +683,139 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>User Provision Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KPMSJ4R0FP05Q2AS6CBBX3DK</t>
+          <t>h_01KPN3327V11YXB95CHXEXJXBT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KPMSJ4R0FP05Q2AS6CBBX3DK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KPN3327V11YXB95CHXEXJXBT</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Create User Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01KGPAMEAW55WS81E8WGSSTNW2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KGPAMEAW55WS81E8WGSSTNW2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Club Number Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>h_01KPN80F9PQZFWJFGYDK4RM8GR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KPN80F9PQZFWJFGYDK4RM8GR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
+          <t>h_01KPMSJ4R0FP05Q2AS6CBBX3DK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KPMSJ4R0FP05Q2AS6CBBX3DK</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Successful Integration Notification Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Failed Integration Notification Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Skipped Integration Notification Settings</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
+          <t>h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Successful Integration Notification Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,164 +847,230 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Failed Integration Notification Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Skipped Integration Notification Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KPMSJ4R0KRGFBZT7S9T8WTDZ</t>
+          <t>h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KPMSJ4R0KRGFBZT7S9T8WTDZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Debug Mode</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KPMSJ4R0KRGFBZT7S9T8WTDZ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KPMSJ4R0KRGFBZT7S9T8WTDZ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/ABC-Fitness-ADP-Lyric-Integration-Guide/headings.xlsx
+++ b/site/ABC-Fitness-ADP-Lyric-Integration-Guide/headings.xlsx
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>User Configuration</t>
+          <t>Worker Configuration</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>User Provision Settings</t>
+          <t>Worker Provision Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Create User Settings</t>
+          <t>Create Worker Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KPN80F9PQZFWJFGYDK4RM8GR</t>
+          <t>h_01KPN9K91KTY4DNPFR4B8SYHJ9</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KPN80F9PQZFWJFGYDK4RM8GR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KPN9K91KTY4DNPFR4B8SYHJ9</t>
         </is>
       </c>
     </row>

--- a/site/ABC-Fitness-ADP-Lyric-Integration-Guide/headings.xlsx
+++ b/site/ABC-Fitness-ADP-Lyric-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Worker Provision Settings</t>
+          <t>Worker Correlation Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Create Worker Settings</t>
+          <t>Worker Provision Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAW55WS81E8WGSSTNW2</t>
+          <t>h_01KQ9PHKY49Z9TV1PETWA3NQ23</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KGPAMEAW55WS81E8WGSSTNW2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KQ9PHKY49Z9TV1PETWA3NQ23</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Club Number Settings</t>
+          <t>Create Worker Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KPN9K91KTY4DNPFR4B8SYHJ9</t>
+          <t>h_01KGPAMEAW55WS81E8WGSSTNW2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KPN9K91KTY4DNPFR4B8SYHJ9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KGPAMEAW55WS81E8WGSSTNW2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Pay Data Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,129 +759,129 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KPMSJ4R0FP05Q2AS6CBBX3DK</t>
+          <t>h_01KRGEFX6C6XWT2WK1GTHHZF4P</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KPMSJ4R0FP05Q2AS6CBBX3DK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KRGEFX6C6XWT2WK1GTHHZF4P</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Worker's Pay Data Correlation Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01KRGJ50TA0XTPCA8DPCKBYYMD</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KRGJ50TA0XTPCA8DPCKBYYMD</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Pay Data Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>h_01KRGJ50TA9SEK9AP25EKKK0ZW</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KRGJ50TA9SEK9AP25EKKK0ZW</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
+          <t>h_01KPMSJ4R0FP05Q2AS6CBBX3DK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KPMSJ4R0FP05Q2AS6CBBX3DK</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Successful Integration Notification Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Failed Integration Notification Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Skipped Integration Notification Settings</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
+          <t>h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Successful Integration Notification Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,164 +913,230 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Failed Integration Notification Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Skipped Integration Notification Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KPMSJ4R0KRGFBZT7S9T8WTDZ</t>
+          <t>h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KPMSJ4R0KRGFBZT7S9T8WTDZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Debug Mode</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KPMSJ4R0KRGFBZT7S9T8WTDZ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01KPMSJ4R0KRGFBZT7S9T8WTDZ</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ABC-Fitness-ADP-Lyric-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
